--- a/data/trans_dic/IP2005-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen los dientes sanos</t>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,47; 95,22</t>
+          <t>83,29; 94,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,65; 99,34</t>
+          <t>93,48; 99,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,29; 100,0</t>
+          <t>97,28; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,2; 87,54</t>
+          <t>69,3; 87,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,08</t>
+          <t>87,04; 96,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,87; 100,0</t>
+          <t>95,32; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,44; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,12; 91,85</t>
+          <t>74,75; 91,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,42; 94,73</t>
+          <t>87,58; 95,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,71; 99,07</t>
+          <t>94,96; 99,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,46; 87,08</t>
+          <t>74,93; 87,02</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 94,77</t>
+          <t>89,51; 94,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,21; 94,78</t>
+          <t>88,26; 94,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,76; 97,02</t>
+          <t>91,49; 96,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,57; 90,72</t>
+          <t>83,06; 91,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,82; 94,2</t>
+          <t>88,86; 94,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,74; 96,04</t>
+          <t>91,02; 96,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,28; 97,65</t>
+          <t>93,54; 97,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,72; 91,87</t>
+          <t>83,38; 91,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,88; 93,94</t>
+          <t>89,99; 93,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,66; 94,73</t>
+          <t>90,75; 94,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,54; 96,83</t>
+          <t>93,45; 96,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,87; 90,38</t>
+          <t>84,49; 90,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,22; 88,24</t>
+          <t>77,32; 88,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,1; 91,69</t>
+          <t>83,33; 92,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,74; 95,2</t>
+          <t>88,71; 95,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,58; 91,55</t>
+          <t>82,72; 91,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,53; 89,22</t>
+          <t>79,41; 88,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,29; 91,05</t>
+          <t>81,92; 91,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,98; 89,02</t>
+          <t>79,82; 88,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,82; 89,94</t>
+          <t>80,87; 90,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79,86; 87,54</t>
+          <t>80,33; 87,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83,76; 90,15</t>
+          <t>84,13; 90,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85,73; 91,03</t>
+          <t>85,63; 91,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,95</t>
+          <t>83,0; 89,41</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,98; 90,43</t>
+          <t>82,94; 90,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,62; 90,25</t>
+          <t>82,39; 90,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,82; 92,61</t>
+          <t>85,31; 92,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,93; 93,11</t>
+          <t>85,68; 93,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,57; 90,23</t>
+          <t>82,51; 89,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,25; 89,56</t>
+          <t>81,18; 89,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,63; 90,78</t>
+          <t>81,8; 90,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,13</t>
+          <t>85,89; 92,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,42; 89,26</t>
+          <t>83,64; 89,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,69; 88,97</t>
+          <t>82,97; 88,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84,99; 90,73</t>
+          <t>85,06; 90,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,46; 92,33</t>
+          <t>87,21; 92,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 90,72</t>
+          <t>86,87; 90,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,24</t>
+          <t>88,19; 92,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,3; 94,61</t>
+          <t>91,45; 94,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,27; 89,93</t>
+          <t>85,5; 90,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 90,79</t>
+          <t>86,73; 90,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,86; 92,5</t>
+          <t>88,92; 92,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,35; 92,87</t>
+          <t>89,16; 92,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,67; 90,08</t>
+          <t>85,44; 90,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,59; 90,24</t>
+          <t>87,41; 90,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,75</t>
+          <t>89,17; 91,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,9; 93,33</t>
+          <t>90,94; 93,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,23; 89,35</t>
+          <t>86,17; 89,43</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>61874</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96119</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>87288</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38701</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77584</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94648</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>40528</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>139457</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>190767</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>167503</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>79229</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>56793; 64692</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>92429; 98216</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85473; 87859</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33854; 42543</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>72900; 80953</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>91433; 95923</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>35827; 43665</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>133065; 144360</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>184969; 192944</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>165193; 168074</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>72518; 84215</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>232185</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>217267</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>198720</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139273</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>231424</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>252192</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>246914</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>159411</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>463608</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>469459</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>445634</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>298683</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>224776; 238541</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208523; 223515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>191962; 203061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>132181; 145422</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>224133; 237887</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>244825; 258470</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>240730; 251462</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>150794; 165468</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>452982; 472738</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>458482; 478164</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>436591; 451920</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>287272; 308138</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>105311</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136172</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>172247</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151614</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>117478</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>137002</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>158802</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>182336</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>222788</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>273174</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>331049</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>333951</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>97598; 111078</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>129358; 142919</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165658; 177957</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143163; 158463</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>110232; 123473</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>128951; 143581</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>149453; 166209</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>171834; 191755</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>212896; 231625</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>263032; 282277</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>320248; 340825</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>320028; 344715</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>165673</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>146930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>246964</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>175960</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>152132</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>150681</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>274816</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>341633</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>299063</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>304362</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>521779</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>158008; 172732</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>140033; 153534</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>146688; 159593</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>236023; 256612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>167890; 182899</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>143898; 159071</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>141803; 157514</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>262370; 283962</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>329499; 352448</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>288075; 308790</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>293695; 313645</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>506615; 536144</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>565042</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>596489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>611937</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576551</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>657092</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1167487</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1232463</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1248548</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1233643</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>552531; 576424</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>582311; 608271</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>600248; 621850</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>561306; 591304</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>588262; 613949</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>622104; 647771</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>622476; 648463</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>638014; 673197</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1148769; 1184449</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1212613; 1249917</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1231855; 1266165</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1209241; 1254989</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2005-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Edad-trans_dic.xlsx
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,29; 94,87</t>
+          <t>83,6; 95,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,48; 99,34</t>
+          <t>92,55; 99,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,28; 100,0</t>
+          <t>96,45; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,3; 87,09</t>
+          <t>69,3; 87,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,04; 96,65</t>
+          <t>87,08; 96,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,32; 100,0</t>
+          <t>95,42; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,75; 91,1</t>
+          <t>75,64; 91,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,58; 95,01</t>
+          <t>87,41; 94,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,96; 99,05</t>
+          <t>95,58; 99,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98,29; 100,0</t>
+          <t>98,61; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,93; 87,02</t>
+          <t>74,89; 87,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,51; 94,99</t>
+          <t>89,28; 94,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,26; 94,61</t>
+          <t>88,32; 94,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,49; 96,78</t>
+          <t>91,5; 96,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,06; 91,38</t>
+          <t>82,83; 91,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,86; 94,32</t>
+          <t>88,49; 94,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,02; 96,09</t>
+          <t>90,98; 96,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,54; 97,71</t>
+          <t>93,57; 97,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,38; 91,49</t>
+          <t>83,94; 91,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,99; 93,92</t>
+          <t>89,87; 93,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,75; 94,64</t>
+          <t>90,7; 94,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,45; 96,73</t>
+          <t>93,68; 96,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,49; 90,63</t>
+          <t>84,72; 90,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,32; 88,0</t>
+          <t>77,57; 88,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,33; 92,07</t>
+          <t>83,17; 91,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,71; 95,29</t>
+          <t>88,85; 95,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,72; 91,56</t>
+          <t>82,77; 91,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,41; 88,95</t>
+          <t>78,9; 89,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,92; 91,21</t>
+          <t>81,92; 90,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,82; 88,77</t>
+          <t>80,21; 89,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,87; 90,24</t>
+          <t>81,22; 90,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,33; 87,39</t>
+          <t>80,64; 87,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,13; 90,29</t>
+          <t>83,66; 90,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85,63; 91,14</t>
+          <t>85,62; 91,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,0; 89,41</t>
+          <t>83,13; 89,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,94; 90,67</t>
+          <t>82,61; 90,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,39; 90,34</t>
+          <t>81,71; 90,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,31; 92,82</t>
+          <t>85,19; 92,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,68; 93,16</t>
+          <t>85,46; 93,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,51; 89,89</t>
+          <t>82,28; 89,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,18; 89,74</t>
+          <t>80,71; 89,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,8; 90,87</t>
+          <t>81,65; 90,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,89; 92,96</t>
+          <t>86,13; 93,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,64; 89,46</t>
+          <t>83,7; 89,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,97; 88,93</t>
+          <t>82,83; 88,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,06; 90,84</t>
+          <t>85,06; 90,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,21; 92,29</t>
+          <t>87,26; 92,12</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,87; 90,63</t>
+          <t>86,62; 90,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,19; 92,12</t>
+          <t>88,22; 92,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,45; 94,74</t>
+          <t>91,5; 94,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,5; 90,07</t>
+          <t>85,57; 90,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,73; 90,52</t>
+          <t>86,82; 90,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,92; 92,59</t>
+          <t>88,93; 92,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,16; 92,88</t>
+          <t>89,27; 92,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,15</t>
+          <t>85,44; 90,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,41; 90,12</t>
+          <t>87,33; 90,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,17; 91,91</t>
+          <t>89,25; 91,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,94; 93,48</t>
+          <t>90,8; 93,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,17; 89,43</t>
+          <t>86,4; 89,63</t>
         </is>
       </c>
     </row>
@@ -1645,32 +1645,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56793; 64692</t>
+          <t>57007; 64967</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92429; 98216</t>
+          <t>91504; 97981</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85473; 87859</t>
+          <t>84736; 87859</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33854; 42543</t>
+          <t>33851; 42502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72900; 80953</t>
+          <t>72936; 80952</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91433; 95923</t>
+          <t>91533; 95923</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1680,27 +1680,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35827; 43665</t>
+          <t>36253; 44022</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133065; 144360</t>
+          <t>132817; 144143</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184969; 192944</t>
+          <t>186177; 193241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165193; 168074</t>
+          <t>165735; 168074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72518; 84215</t>
+          <t>72481; 84390</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>224776; 238541</t>
+          <t>224218; 238098</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>208523; 223515</t>
+          <t>208647; 223265</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191962; 203061</t>
+          <t>191992; 203374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132181; 145422</t>
+          <t>131811; 145420</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>224133; 237887</t>
+          <t>223184; 237353</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244825; 258470</t>
+          <t>244729; 258298</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>240730; 251462</t>
+          <t>240809; 251363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>150794; 165468</t>
+          <t>151810; 165859</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>452982; 472738</t>
+          <t>452349; 472311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>458482; 478164</t>
+          <t>458243; 477733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>436591; 451920</t>
+          <t>437656; 452647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>287272; 308138</t>
+          <t>288027; 308129</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97598; 111078</t>
+          <t>97914; 111161</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>129358; 142919</t>
+          <t>129104; 142547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165658; 177957</t>
+          <t>165922; 177654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143163; 158463</t>
+          <t>143255; 158659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>110232; 123473</t>
+          <t>109532; 123602</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>128951; 143581</t>
+          <t>128950; 143144</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149453; 166209</t>
+          <t>150178; 166802</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>171834; 191755</t>
+          <t>172588; 191671</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212896; 231625</t>
+          <t>213726; 231533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>263032; 282277</t>
+          <t>261568; 282045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320248; 340825</t>
+          <t>320219; 340904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>320028; 344715</t>
+          <t>320500; 344962</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>158008; 172732</t>
+          <t>157367; 172488</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>140033; 153534</t>
+          <t>138877; 153571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146688; 159593</t>
+          <t>146471; 159532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>236023; 256612</t>
+          <t>235394; 256623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>167890; 182899</t>
+          <t>167407; 182962</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143898; 159071</t>
+          <t>143075; 158495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>141803; 157514</t>
+          <t>141540; 157312</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>262370; 283962</t>
+          <t>263108; 284994</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>329499; 352448</t>
+          <t>329770; 352087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288075; 308790</t>
+          <t>287620; 308658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293695; 313645</t>
+          <t>293713; 313761</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>506615; 536144</t>
+          <t>506920; 535162</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>552531; 576424</t>
+          <t>550920; 577113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>582311; 608271</t>
+          <t>582533; 607939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>600248; 621850</t>
+          <t>600600; 621485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561306; 591304</t>
+          <t>561769; 591434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>588262; 613949</t>
+          <t>588853; 615466</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622104; 647771</t>
+          <t>622114; 647513</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>622476; 648463</t>
+          <t>623220; 648223</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638014; 673197</t>
+          <t>638033; 672062</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1148769; 1184449</t>
+          <t>1147811; 1183551</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1212613; 1249917</t>
+          <t>1213770; 1248925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1231855; 1266165</t>
+          <t>1229970; 1263683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1209241; 1254989</t>
+          <t>1212458; 1257706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2005-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>97,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,6; 95,28</t>
+          <t>86,76; 96,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,55; 99,1</t>
+          <t>95,87; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,45; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,3; 87,01</t>
+          <t>75,38; 91,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,08; 96,65</t>
+          <t>84,47; 95,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,42; 100,0</t>
+          <t>93,65; 99,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,29; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,64; 91,85</t>
+          <t>69,14; 87,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,41; 94,87</t>
+          <t>87,42; 94,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,58; 99,2</t>
+          <t>95,71; 99,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98,61; 100,0</t>
+          <t>98,29; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,89; 87,2</t>
+          <t>74,6; 86,72</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88,02%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>92,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>94,71%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,28; 94,81</t>
+          <t>88,82; 94,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,32; 94,5</t>
+          <t>90,74; 96,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,5; 96,93</t>
+          <t>93,28; 97,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,83; 91,38</t>
+          <t>83,45; 91,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,49; 94,1</t>
+          <t>89,3; 94,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,98; 96,02</t>
+          <t>88,21; 94,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,57; 97,67</t>
+          <t>91,76; 97,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,94; 91,71</t>
+          <t>81,88; 90,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,87; 93,83</t>
+          <t>89,88; 93,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,7; 94,56</t>
+          <t>90,66; 94,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,68; 96,89</t>
+          <t>93,54; 96,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,72; 90,63</t>
+          <t>84,52; 90,3</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84,82%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>83,43%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>87,72%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>92,23%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,57; 88,07</t>
+          <t>79,53; 89,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,17; 91,83</t>
+          <t>82,29; 91,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,85; 95,13</t>
+          <t>79,98; 89,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,77; 91,67</t>
+          <t>80,77; 89,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,9; 89,04</t>
+          <t>77,22; 88,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,92; 90,93</t>
+          <t>83,1; 91,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,21; 89,09</t>
+          <t>88,74; 95,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,22; 90,2</t>
+          <t>81,75; 91,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,64; 87,36</t>
+          <t>79,86; 87,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83,66; 90,21</t>
+          <t>83,76; 90,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85,62; 91,16</t>
+          <t>85,73; 91,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,13; 89,47</t>
+          <t>83,24; 89,62</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>86,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>86,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>86,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>89,38%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,54</t>
+          <t>82,57; 90,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,71; 90,36</t>
+          <t>81,25; 89,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,19; 92,78</t>
+          <t>81,63; 90,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,46; 93,16</t>
+          <t>85,83; 93,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,28; 89,92</t>
+          <t>82,98; 90,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,71; 89,41</t>
+          <t>81,62; 90,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,65; 90,75</t>
+          <t>84,82; 92,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,13; 93,29</t>
+          <t>84,87; 91,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,7; 89,37</t>
+          <t>83,42; 89,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,83; 88,89</t>
+          <t>82,69; 88,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,06; 90,87</t>
+          <t>84,99; 90,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,26; 92,12</t>
+          <t>86,93; 91,71</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,62; 90,74</t>
+          <t>86,69; 90,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,07</t>
+          <t>88,86; 92,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,5; 94,68</t>
+          <t>89,35; 92,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,09</t>
+          <t>85,52; 90,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,82; 90,74</t>
+          <t>86,8; 90,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,93; 92,56</t>
+          <t>88,31; 92,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 92,85</t>
+          <t>91,3; 94,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,0</t>
+          <t>84,68; 89,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 90,05</t>
+          <t>87,59; 90,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,84</t>
+          <t>89,25; 91,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,8; 93,29</t>
+          <t>90,9; 93,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,4; 89,63</t>
+          <t>85,92; 88,99</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77584</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>94648</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33389</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>61874</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96119</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>87288</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38701</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>77584</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94648</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79229</t>
+          <t>68833</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57007; 64967</t>
+          <t>72664; 80473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91504; 97981</t>
+          <t>91961; 95923</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84736; 87859</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33851; 42502</t>
+          <t>29907; 36131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72936; 80952</t>
+          <t>57597; 64926</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91533; 95923</t>
+          <t>92593; 98220</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84602; 87859</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36253; 44022</t>
+          <t>31061; 39248</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132817; 144143</t>
+          <t>132827; 143940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186177; 193241</t>
+          <t>186443; 192975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165735; 168074</t>
+          <t>165208; 168074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72481; 84390</t>
+          <t>63110; 73363</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>315</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>315</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>223</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>231424</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252192</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>246914</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>137425</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>232185</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>217267</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>198720</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139273</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>231424</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>252192</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>246914</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>126159</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>298683</t>
+          <t>263585</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>224218; 238098</t>
+          <t>224016; 237592</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>208647; 223265</t>
+          <t>244071; 258352</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191992; 203374</t>
+          <t>240073; 251321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131811; 145420</t>
+          <t>130290; 143383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>223184; 237353</t>
+          <t>224262; 238004</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244729; 258298</t>
+          <t>208397; 223920</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>240809; 251363</t>
+          <t>192540; 203567</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>151810; 165859</t>
+          <t>118749; 131084</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>452349; 472311</t>
+          <t>452413; 472870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>458243; 477733</t>
+          <t>458063; 478640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>437656; 452647</t>
+          <t>437023; 452362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>288027; 308129</t>
+          <t>254532; 271954</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>204</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117478</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158802</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171202</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>105311</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>136172</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>172247</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>151614</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>117478</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>137002</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>158802</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>182336</t>
+          <t>152099</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>333951</t>
+          <t>323301</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97914; 111161</t>
+          <t>110398; 123855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>129104; 142547</t>
+          <t>129530; 143328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165922; 177654</t>
+          <t>149751; 166664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143255; 158659</t>
+          <t>161635; 179667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109532; 123602</t>
+          <t>97474; 111382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>128950; 143144</t>
+          <t>129002; 142337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>150178; 166802</t>
+          <t>165725; 177784</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>172588; 191671</t>
+          <t>142795; 159275</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>213726; 231533</t>
+          <t>211646; 232001</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>261568; 282045</t>
+          <t>261866; 281853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320219; 340904</t>
+          <t>320625; 340431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>320500; 344962</t>
+          <t>311985; 335894</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>303</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>175960</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>152132</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>150681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>263440</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>165673</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>146930</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>153681</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>246964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>175960</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>152132</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>150681</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>274816</t>
+          <t>227884</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>521779</t>
+          <t>491324</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157367; 172488</t>
+          <t>168015; 183594</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138877; 153571</t>
+          <t>144029; 158749</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146471; 159532</t>
+          <t>141501; 157371</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>235394; 256623</t>
+          <t>251172; 272591</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>167407; 182962</t>
+          <t>158073; 172268</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143075; 158495</t>
+          <t>138716; 153393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>141540; 157312</t>
+          <t>145843; 159243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>263108; 284994</t>
+          <t>217746; 235530</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>329770; 352087</t>
+          <t>328642; 351676</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>287620; 308658</t>
+          <t>287120; 308924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293713; 313761</t>
+          <t>293454; 313292</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>506920; 535162</t>
+          <t>477414; 503653</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>861</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>804</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>576551</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>635974</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1233643</t>
+          <t>1147041</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>550920; 577113</t>
+          <t>588001; 615775</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>582533; 607939</t>
+          <t>621627; 647096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>600600; 621485</t>
+          <t>623795; 648383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561769; 591434</t>
+          <t>588897; 619965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>588853; 615466</t>
+          <t>552078; 577011</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622114; 647513</t>
+          <t>583154; 609046</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>623220; 648223</t>
+          <t>599300; 621013</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638033; 672062</t>
+          <t>526008; 553879</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1147811; 1183551</t>
+          <t>1151246; 1186030</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1213770; 1248925</t>
+          <t>1213678; 1247739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1229970; 1263683</t>
+          <t>1231256; 1264212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1212458; 1257706</t>
+          <t>1125379; 1165551</t>
         </is>
       </c>
     </row>
